--- a/data/gravel/Mondraker Chrono Carbon DC 2025.xlsx
+++ b/data/gravel/Mondraker Chrono Carbon DC 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610CCA12-57AE-EB4D-B654-E17994867D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0230937-9629-F343-8834-F18EA3F100E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10120" yWindow="2200" windowWidth="26640" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2200" windowWidth="26640" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1342,10 +1342,16 @@
       <c r="A44" t="s">
         <v>35</v>
       </c>
+      <c r="B44">
+        <v>120</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
+      </c>
+      <c r="B45">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
